--- a/intake_forms/029_expense_recovery_program_application_form--intake_forms.xlsx
+++ b/intake_forms/029_expense_recovery_program_application_form--intake_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1083,8 +1083,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'business_trip',_'value':_'business_trip'}</t>
+          <t>business_trip</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'Business Trip', 'value': 'business_trip'}</t>
+          <t>Business Trip</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'business_meeting',_'value':_'business_meeting'}</t>
+          <t>business_meeting</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Business Meeting', 'value': 'business_meeting'}</t>
+          <t>Business Meeting</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_'jane_doe',_'value':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': 'Jane Doe', 'value': 'jane_doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_16,_'label':_'john_doe',_'value':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 16, 'label': 'John Doe', 'value': 'john_doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_17,_'label':_'jane_doe',_'value':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 17, 'label': 'Jane Doe', 'value': 'jane_doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_18,_'label':_'john_doe',_'value':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 18, 'label': 'John Doe', 'value': 'john_doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_19,_'label':_'jane_doe',_'value':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 19, 'label': 'Jane Doe', 'value': 'jane_doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_20,_'label':_'john_doe',_'value':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 20, 'label': 'John Doe', 'value': 'john_doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
